--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="Q2" t="n">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="R2" t="n">
-        <v>3236</v>
+        <v>3246</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>1064</v>
       </c>
       <c r="Q3" t="n">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="R3" t="n">
-        <v>3526</v>
+        <v>3528</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q5" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="R5" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피버짐24 헬스&amp;PT 남외점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fevergym2022@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1435-7701</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 중구 남외2길 30 5층</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fevergym2022</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dc7c</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="Q6" t="n">
-        <v>971</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>1406</v>
+        <v>510</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1418697718</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418697718</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>각성짐 삼산점</t>
+          <t>더브로짐 호계매곡점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gacksung_gym@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1385-3827</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 돋질로 292 2층,3층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gacksung_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi9p345</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>389</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="n">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>514</v>
+        <v>157</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1473626995</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473626995</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2206</v>
+        <v>168</v>
       </c>
       <c r="Q8" t="n">
-        <v>498</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>2704</v>
+        <v>212</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>각성짐 명촌점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>gacksunggym2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1393-3411</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 북구 명촌10길 3 3, 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>https://blog.naver.com/gacksunggym2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,22 +1287,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>445</v>
+        <v>220</v>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>509</v>
+        <v>229</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>2068878335</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/2068878335</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더브로짐 호계매곡점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w423pi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>60</v>
+        <v>1019</v>
       </c>
       <c r="Q10" t="n">
-        <v>96</v>
+        <v>467</v>
       </c>
       <c r="R10" t="n">
-        <v>156</v>
+        <v>1486</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,39 +1437,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1479,19 +1479,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1070</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>1928</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>2998</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1348</v>
+        <v>1383</v>
       </c>
       <c r="Q2" t="n">
-        <v>1898</v>
+        <v>1976</v>
       </c>
       <c r="R2" t="n">
-        <v>3246</v>
+        <v>3359</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="Q3" t="n">
-        <v>2464</v>
+        <v>2510</v>
       </c>
       <c r="R3" t="n">
-        <v>3528</v>
+        <v>3579</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>나인스짐 헬스&amp;PT 달동점</t>
+          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ninesgym@naver.com</t>
+          <t>newfit_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1478-9926</t>
+          <t>0507-1308-7701</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 150 유수빌딩 2층</t>
+          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://ninesgym.wixsite.com/ninesgym</t>
+          <t>https://blog.naver.com/newfit_5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ve26</t>
+          <t>https://talk.naver.com/ct/w4unvk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>754</v>
+        <v>2323</v>
       </c>
       <c r="Q4" t="n">
-        <v>334</v>
+        <v>1415</v>
       </c>
       <c r="R4" t="n">
-        <v>1088</v>
+        <v>3738</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1277473221</t>
+          <t>1197677944</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277473221</t>
+          <t>https://m.place.naver.com/place/1197677944</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,39 +858,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>유짐휘트니스 화봉점</t>
+          <t>마인드휘트니스 송정점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yoogym_hb@naver.com</t>
+          <t>mindfitness8@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1432-8232</t>
+          <t>0507-1340-0798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 북구 화산중앙로 84 4층</t>
+          <t>울산 북구 박상진12로 11 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yoogym_hb/224136677424</t>
+          <t>https://mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w8u9</t>
+          <t>https://talk.naver.com/ct/w4ja8b</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>342</v>
+        <v>1795</v>
       </c>
       <c r="Q5" t="n">
-        <v>299</v>
+        <v>605</v>
       </c>
       <c r="R5" t="n">
-        <v>641</v>
+        <v>2400</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37829508</t>
+          <t>1581714429</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37829508</t>
+          <t>https://m.place.naver.com/place/1581714429</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>각성짐 삼산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>gacksung_gym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1385-3827</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 남구 돋질로 292 2층,3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>https://blog.naver.com/gacksung_gym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,22 +993,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>446</v>
+        <v>396</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="R6" t="n">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>1473626995</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/1473626995</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더브로짐 호계매곡점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>60</v>
+        <v>2227</v>
       </c>
       <c r="Q7" t="n">
-        <v>97</v>
+        <v>508</v>
       </c>
       <c r="R7" t="n">
-        <v>157</v>
+        <v>2735</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>168</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>각성짐 명촌점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gacksunggym2@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1393-3411</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 북구 명촌10길 3 3, 4층</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gacksunggym2</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,18 +1283,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e9we</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>220</v>
+        <v>457</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="R9" t="n">
-        <v>229</v>
+        <v>528</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2068878335</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068878335</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>63</v>
       </c>
       <c r="Q10" t="n">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="R10" t="n">
-        <v>1486</v>
+        <v>168</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="Q11" t="n">
-        <v>1928</v>
+        <v>1970</v>
       </c>
       <c r="R11" t="n">
-        <v>2998</v>
+        <v>3050</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="Q2" t="n">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="R2" t="n">
-        <v>3359</v>
+        <v>3376</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>1069</v>
       </c>
       <c r="Q3" t="n">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="R3" t="n">
-        <v>3579</v>
+        <v>3583</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
+          <t>나인스짐 헬스&amp;PT 달동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>newfit_5@naver.com</t>
+          <t>ninesgym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1308-7701</t>
+          <t>0507-1478-9926</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
+          <t>울산 남구 삼산로 150 유수빌딩 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_5</t>
+          <t>https://ninesgym.wixsite.com/ninesgym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4unvk</t>
+          <t>https://talk.naver.com/ct/w5ve26</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2323</v>
+        <v>767</v>
       </c>
       <c r="Q4" t="n">
-        <v>1415</v>
+        <v>336</v>
       </c>
       <c r="R4" t="n">
-        <v>3738</v>
+        <v>1103</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1197677944</t>
+          <t>1277473221</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197677944</t>
+          <t>https://m.place.naver.com/place/1277473221</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="Q5" t="n">
         <v>605</v>
       </c>
       <c r="R5" t="n">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>각성짐 삼산점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gacksung_gym@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1385-3827</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 돋질로 292 2층,3층</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gacksung_gym</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ujg</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>396</v>
+        <v>2228</v>
       </c>
       <c r="Q6" t="n">
-        <v>126</v>
+        <v>508</v>
       </c>
       <c r="R6" t="n">
-        <v>522</v>
+        <v>2736</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1473626995</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473626995</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2227</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>508</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
-        <v>2735</v>
+        <v>31</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1195,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>457</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>529</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1293,27 +1297,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>457</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="R9" t="n">
-        <v>528</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="Q11" t="n">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="R11" t="n">
-        <v>3050</v>
+        <v>3062</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1524,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -628,10 +628,10 @@
         <v>1391</v>
       </c>
       <c r="Q2" t="n">
-        <v>1985</v>
+        <v>1991</v>
       </c>
       <c r="R2" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>1084</v>
       </c>
       <c r="Q11" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="R11" t="n">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>1391</v>
       </c>
       <c r="Q2" t="n">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="R2" t="n">
-        <v>3382</v>
+        <v>3390</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness1/223603908662</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="Q3" t="n">
         <v>2519</v>
       </c>
       <c r="R3" t="n">
-        <v>3589</v>
+        <v>3590</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>459</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="R6" t="n">
-        <v>531</v>
+        <v>32</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,24 +1054,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>63</v>
+        <v>459</v>
       </c>
       <c r="Q7" t="n">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="R7" t="n">
-        <v>168</v>
+        <v>531</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="R8" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1031</v>
+        <v>181</v>
       </c>
       <c r="Q9" t="n">
-        <v>459</v>
+        <v>54</v>
       </c>
       <c r="R9" t="n">
-        <v>1490</v>
+        <v>235</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,23 +1380,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423pi</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>126</v>
+        <v>1031</v>
       </c>
       <c r="Q10" t="n">
-        <v>300</v>
+        <v>459</v>
       </c>
       <c r="R10" t="n">
-        <v>426</v>
+        <v>1490</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/huntfitness1/223603908662</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -978,17 +978,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>26</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -726,10 +726,10 @@
         <v>1071</v>
       </c>
       <c r="Q3" t="n">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="R3" t="n">
-        <v>3590</v>
+        <v>3593</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,39 +760,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마인드휘트니스 송정점</t>
+          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mindfitness8@naver.com</t>
+          <t>newfit_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1340-0798</t>
+          <t>0507-1308-7701</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 북구 박상진12로 11 8층</t>
+          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://mindfitness-official.com/</t>
+          <t>https://blog.naver.com/newfit_5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ja8b</t>
+          <t>https://talk.naver.com/ct/w4unvk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1797</v>
+        <v>2324</v>
       </c>
       <c r="Q4" t="n">
-        <v>605</v>
+        <v>1415</v>
       </c>
       <c r="R4" t="n">
-        <v>2402</v>
+        <v>3739</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1581714429</t>
+          <t>1197677944</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581714429</t>
+          <t>https://m.place.naver.com/place/1197677944</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>나인스짐 헬스&amp;PT 달동점</t>
+          <t>마인드휘트니스 송정점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ninesgym@naver.com</t>
+          <t>mindfitness8@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1478-9926</t>
+          <t>0507-1340-0798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 150 유수빌딩 2층</t>
+          <t>울산 북구 박상진12로 11 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://ninesgym.wixsite.com/ninesgym</t>
+          <t>https://mindfitness-official.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ve26</t>
+          <t>https://talk.naver.com/ct/w4ja8b</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>767</v>
+        <v>1797</v>
       </c>
       <c r="Q5" t="n">
-        <v>336</v>
+        <v>606</v>
       </c>
       <c r="R5" t="n">
-        <v>1103</v>
+        <v>2403</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1277473221</t>
+          <t>1581714429</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277473221</t>
+          <t>https://m.place.naver.com/place/1581714429</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>2228</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>510</v>
       </c>
       <c r="R6" t="n">
-        <v>33</v>
+        <v>2738</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>459</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
-        <v>531</v>
+        <v>33</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>459</v>
       </c>
       <c r="Q8" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="R8" t="n">
-        <v>168</v>
+        <v>532</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>더브로짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>as1458@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1479-8856</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/wi9p345</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="R9" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>1558775598</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/1558775598</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1031</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>459</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>1490</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q11" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="R11" t="n">
-        <v>3070</v>
+        <v>3075</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="Q3" t="n">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="R3" t="n">
-        <v>3593</v>
+        <v>3598</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT야음점</t>
+          <t>모모짐 24헬스&amp;PT 달동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bemoveyaeum@naver.com</t>
+          <t>momogym-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1386-7929</t>
+          <t>0507-1343-6807</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
+          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bemoveyaeum</t>
+          <t>https://www.instagram.com/momogym.xx</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ujg</t>
+          <t>https://talk.naver.com/ct/wxpbega</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2228</v>
+        <v>120</v>
       </c>
       <c r="Q6" t="n">
-        <v>510</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>2738</v>
+        <v>149</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1092788853</t>
+          <t>2064303253</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092788853</t>
+          <t>https://m.place.naver.com/place/2064303253</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>459</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="R7" t="n">
-        <v>33</v>
+        <v>532</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>https://blog.naver.com/fitpointgym24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>459</v>
+        <v>181</v>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="R8" t="n">
-        <v>532</v>
+        <v>236</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>2023664509</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/2023664509</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더브로짐 신천점</t>
+          <t>비무브짐24 헬스&amp;PT 병영점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>as1458@naver.com</t>
+          <t>bm_team_leader@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1479-8856</t>
+          <t>0507-1359-7929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 북구 제내1길 2 402, 403, 404, 408호</t>
+          <t>울산 중구 번영로 564 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bm_team_leader</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi9p345</t>
+          <t>https://talk.naver.com/ct/w423pi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>63</v>
+        <v>1032</v>
       </c>
       <c r="Q9" t="n">
-        <v>105</v>
+        <v>459</v>
       </c>
       <c r="R9" t="n">
-        <v>168</v>
+        <v>1491</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1558775598</t>
+          <t>1653136712</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558775598</t>
+          <t>https://m.place.naver.com/place/1653136712</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>휘트니스클리닉 울산동구점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>fitnessclinic_ulsan1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1304-6479</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 동구 대학길 30 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1390,17 +1390,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>300</v>
       </c>
       <c r="R10" t="n">
-        <v>235</v>
+        <v>426</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>242237435</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/242237435</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Q11" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="R11" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1528,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="Q2" t="n">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="R2" t="n">
-        <v>3390</v>
+        <v>3399</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헌트피트니스 삼산점</t>
+          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>huntfitness1@naver.com</t>
+          <t>newfit_5@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1347-1553</t>
+          <t>0507-1308-7701</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
+          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness1/223603908662</t>
+          <t>https://blog.naver.com/newfit_5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4it5s</t>
+          <t>https://talk.naver.com/ct/w4unvk</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1074</v>
+        <v>2326</v>
       </c>
       <c r="Q3" t="n">
-        <v>2524</v>
+        <v>1416</v>
       </c>
       <c r="R3" t="n">
-        <v>3598</v>
+        <v>3742</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1987440572</t>
+          <t>1197677944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987440572</t>
+          <t>https://m.place.naver.com/place/1197677944</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
+          <t>헌트피트니스 삼산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>newfit_5@naver.com</t>
+          <t>huntfitness1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1308-7701</t>
+          <t>0507-1347-1553</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
+          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_5</t>
+          <t>https://blog.naver.com/huntfitness1/223603908662</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4unvk</t>
+          <t>https://talk.naver.com/ct/w4it5s</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2324</v>
+        <v>1076</v>
       </c>
       <c r="Q4" t="n">
-        <v>1415</v>
+        <v>2527</v>
       </c>
       <c r="R4" t="n">
-        <v>3739</v>
+        <v>3603</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1197677944</t>
+          <t>1987440572</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197677944</t>
+          <t>https://m.place.naver.com/place/1987440572</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="Q5" t="n">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="R5" t="n">
         <v>2403</v>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>모모짐 24헬스&amp;PT 달동점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>momogym-@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1343-6807</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momogym.xx</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxpbega</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2064303253</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064303253</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R8" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q9" t="n">
         <v>459</v>
       </c>
       <c r="R9" t="n">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1408,10 +1408,10 @@
         <v>126</v>
       </c>
       <c r="Q10" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="Q11" t="n">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="R11" t="n">
-        <v>3077</v>
+        <v>3081</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
+          <t>헌트피트니스 삼산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ditegym@naver.com</t>
+          <t>huntfitness1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1446-8926</t>
+          <t>0507-1347-1553</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 234 4층 401호</t>
+          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://ditegym.com/</t>
+          <t>https://blog.naver.com/huntfitness1/223603908662</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkujcar</t>
+          <t>https://talk.naver.com/ct/w4it5s</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1394</v>
+        <v>1078</v>
       </c>
       <c r="Q2" t="n">
-        <v>2005</v>
+        <v>2527</v>
       </c>
       <c r="R2" t="n">
-        <v>3399</v>
+        <v>3605</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1071156655</t>
+          <t>1987440572</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071156655</t>
+          <t>https://m.place.naver.com/place/1987440572</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
+          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>newfit_5@naver.com</t>
+          <t>ditegym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1308-7701</t>
+          <t>0507-1446-8926</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
+          <t>울산 남구 번영로 234 4층 401호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_5</t>
+          <t>https://ditegym.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4unvk</t>
+          <t>https://talk.naver.com/ct/wkujcar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2326</v>
+        <v>1396</v>
       </c>
       <c r="Q3" t="n">
-        <v>1416</v>
+        <v>2005</v>
       </c>
       <c r="R3" t="n">
-        <v>3742</v>
+        <v>3401</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1197677944</t>
+          <t>1071156655</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197677944</t>
+          <t>https://m.place.naver.com/place/1071156655</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헌트피트니스 삼산점</t>
+          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>huntfitness1@naver.com</t>
+          <t>newfit_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-1553</t>
+          <t>0507-1308-7701</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
+          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness1/223603908662</t>
+          <t>https://blog.naver.com/newfit_5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4it5s</t>
+          <t>https://talk.naver.com/ct/w4unvk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1076</v>
+        <v>2327</v>
       </c>
       <c r="Q4" t="n">
-        <v>2527</v>
+        <v>1416</v>
       </c>
       <c r="R4" t="n">
-        <v>3603</v>
+        <v>3743</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1987440572</t>
+          <t>1197677944</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987440572</t>
+          <t>https://m.place.naver.com/place/1197677944</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이온짐 울산송정점</t>
+          <t>모모짐 24헬스&amp;PT 달동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eongymsj@naver.com</t>
+          <t>momogym-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1312-6638</t>
+          <t>0507-1343-6807</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
+          <t>울산 남구 도산로 45 2층 모모짐 (MOMOGYM)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://naver.me/xsZ4HAre</t>
+          <t>https://www.instagram.com/momogym.xx</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w35nguy</t>
+          <t>https://talk.naver.com/ct/wxpbega</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2013972444</t>
+          <t>2064303253</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013972444</t>
+          <t>https://m.place.naver.com/place/2064303253</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더메이커짐 울산점</t>
+          <t>비무브짐24 헬스&amp;PT야음점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>themakergymulsan@naver.com</t>
+          <t>bemoveyaeum@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1389-9391</t>
+          <t>0507-1386-7929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
+          <t>울산 남구 수암로128번길 14 수암 회센터 건물 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https:///open.kakao.com/o/sY40o5hf</t>
+          <t>https://blog.naver.com/bemoveyaeum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e9we</t>
+          <t>https://talk.naver.com/ct/w40ujg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>459</v>
+        <v>2231</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>510</v>
       </c>
       <c r="R7" t="n">
-        <v>532</v>
+        <v>2741</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1907598098</t>
+          <t>1092788853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907598098</t>
+          <t>https://m.place.naver.com/place/1092788853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>핏포인트짐24 헬스&amp;PT달동점</t>
+          <t>이온짐 울산송정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitpointgym24@naver.com</t>
+          <t>eongymsj@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1369-1554</t>
+          <t>0507-1312-6638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+          <t>울산 북구 화산로 123 901호, 902호, 903호, 904호, 905호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitpointgym24</t>
+          <t>https://naver.me/xsZ4HAre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9eb6zq</t>
+          <t>https://talk.naver.com/ct/w35nguy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="R8" t="n">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2023664509</t>
+          <t>2013972444</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023664509</t>
+          <t>https://m.place.naver.com/place/2013972444</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 병영점</t>
+          <t>더메이커짐 울산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bm_team_leader@naver.com</t>
+          <t>themakergymulsan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-7929</t>
+          <t>0507-1389-9391</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 중구 번영로 564 10층</t>
+          <t>울산 남구 울밀로 2906 한솔애플타워 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bm_team_leader</t>
+          <t>https:///open.kakao.com/o/sY40o5hf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423pi</t>
+          <t>https://talk.naver.com/ct/w4e9we</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1033</v>
+        <v>459</v>
       </c>
       <c r="Q9" t="n">
-        <v>459</v>
+        <v>73</v>
       </c>
       <c r="R9" t="n">
-        <v>1492</v>
+        <v>532</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1653136712</t>
+          <t>1907598098</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653136712</t>
+          <t>https://m.place.naver.com/place/1907598098</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스클리닉 울산동구점</t>
+          <t>헌트피트니스 옥동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitnessclinic_ulsan1@naver.com</t>
+          <t>huntfitness_2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-6479</t>
+          <t>0507-1422-1553</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 동구 대학길 30 지하1층</t>
+          <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclinic_ulsan1</t>
+          <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>126</v>
+        <v>1092</v>
       </c>
       <c r="Q10" t="n">
-        <v>301</v>
+        <v>1990</v>
       </c>
       <c r="R10" t="n">
-        <v>427</v>
+        <v>3082</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,111 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>242237435</t>
+          <t>1960233397</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/242237435</t>
+          <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>헌트피트니스 옥동점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>huntfitness_2@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1422-1553</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>울산 남구 동산로29번길 4 2-3층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/huntfitness_2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1091</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1990</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3081</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1960233397</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1960233397</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/울산_헬스장.xlsx
+++ b/naver-place-crawler/results_health/울산_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헌트피트니스 삼산점</t>
+          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>huntfitness1@naver.com</t>
+          <t>ditegym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1347-1553</t>
+          <t>0507-1446-8926</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
+          <t>울산 남구 번영로 234 4층 401호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huntfitness1/223603908662</t>
+          <t>https://ditegym.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4it5s</t>
+          <t>https://talk.naver.com/ct/wkujcar</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1078</v>
+        <v>1396</v>
       </c>
       <c r="Q2" t="n">
-        <v>2527</v>
+        <v>2011</v>
       </c>
       <c r="R2" t="n">
-        <v>3605</v>
+        <v>3407</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1987440572</t>
+          <t>1071156655</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987440572</t>
+          <t>https://m.place.naver.com/place/1071156655</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이트짐 헬스&amp;PT 울산삼산본점</t>
+          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ditegym@naver.com</t>
+          <t>newfit_5@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1446-8926</t>
+          <t>0507-1308-7701</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>울산 남구 번영로 234 4층 401호</t>
+          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://ditegym.com/</t>
+          <t>https://blog.naver.com/newfit_5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkujcar</t>
+          <t>https://talk.naver.com/ct/w4unvk</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1396</v>
+        <v>2327</v>
       </c>
       <c r="Q3" t="n">
-        <v>2005</v>
+        <v>1416</v>
       </c>
       <c r="R3" t="n">
-        <v>3401</v>
+        <v>3743</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1071156655</t>
+          <t>1197677944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071156655</t>
+          <t>https://m.place.naver.com/place/1197677944</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뉴핏휘트니스 뉴코아아울렛 울산점</t>
+          <t>헌트피트니스 삼산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>newfit_5@naver.com</t>
+          <t>huntfitness1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1308-7701</t>
+          <t>0507-1347-1553</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>울산 남구 삼산로 217 뉴코아아울렛 12층</t>
+          <t>울산 남구 삼산로 274 W-센터 3층 헌트피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newfit_5</t>
+          <t>https://blog.naver.com/huntfitness1/223603908662</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4unvk</t>
+          <t>https://talk.naver.com/ct/w4it5s</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2327</v>
+        <v>1078</v>
       </c>
       <c r="Q4" t="n">
-        <v>1416</v>
+        <v>2527</v>
       </c>
       <c r="R4" t="n">
-        <v>3743</v>
+        <v>3605</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1197677944</t>
+          <t>1987440572</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197677944</t>
+          <t>https://m.place.naver.com/place/1987440572</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1343,92 +1343,190 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헌트피트니스 옥동점</t>
+          <t>핏포인트짐24 헬스&amp;PT달동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>huntfitness_2@naver.com</t>
+          <t>fitpointgym24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1422-1553</t>
+          <t>0507-1369-1554</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>울산 남구 삼산로 100 화상병원건물 4층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitpointgym24</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9eb6zq</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57</v>
+      </c>
+      <c r="R10" t="n">
+        <v>240</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2023664509</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023664509</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>헌트피트니스 옥동점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>huntfitness_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1422-1553</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>울산 남구 동산로29번길 4 2-3층</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://blog.naver.com/huntfitness_2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>1092</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>1990</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>3082</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1960233397</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1960233397</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
